--- a/godot/application/internationality/internationality.xlsx
+++ b/godot/application/internationality/internationality.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="321">
   <si>
     <t>KEYS</t>
   </si>
@@ -92,121 +92,115 @@
     <t>environment_configuration</t>
   </si>
   <si>
-    <t>Environment configuration</t>
-  </si>
-  <si>
-    <t>环境配置</t>
-  </si>
-  <si>
-    <t>環境配置</t>
-  </si>
-  <si>
-    <t>環境設定</t>
-  </si>
-  <si>
-    <t>환경 구성</t>
-  </si>
-  <si>
-    <t>Umgebungskonfiguration</t>
-  </si>
-  <si>
-    <t>Configuration de l'environnement</t>
-  </si>
-  <si>
-    <t>Configuración del entorno</t>
-  </si>
-  <si>
-    <t>Configurazione ambiente</t>
+    <t>configuration</t>
+  </si>
+  <si>
+    <t>配置</t>
+  </si>
+  <si>
+    <t>構成</t>
+  </si>
+  <si>
+    <t>구성</t>
+  </si>
+  <si>
+    <t>Konfiguration</t>
+  </si>
+  <si>
+    <t>Configuration</t>
+  </si>
+  <si>
+    <t>Configuración</t>
+  </si>
+  <si>
+    <t>Configurazione</t>
   </si>
   <si>
     <t>project_creation</t>
   </si>
   <si>
-    <t>Project creation</t>
-  </si>
-  <si>
-    <t>项目创建</t>
-  </si>
-  <si>
-    <t>專案創建</t>
-  </si>
-  <si>
-    <t>プロジェクト作成</t>
-  </si>
-  <si>
-    <t>프로젝트 생성</t>
-  </si>
-  <si>
-    <t>Projekterstellung</t>
-  </si>
-  <si>
-    <t>Création de projet</t>
-  </si>
-  <si>
-    <t>Creación de proyectos</t>
-  </si>
-  <si>
-    <t>Creazione del progetto</t>
+    <t>project</t>
+  </si>
+  <si>
+    <t>项目</t>
+  </si>
+  <si>
+    <t>專案</t>
+  </si>
+  <si>
+    <t>プロジェクト</t>
+  </si>
+  <si>
+    <t>프로젝트</t>
+  </si>
+  <si>
+    <t>Projekt</t>
+  </si>
+  <si>
+    <t>projet</t>
+  </si>
+  <si>
+    <t>proyecto</t>
+  </si>
+  <si>
+    <t>progetto</t>
   </si>
   <si>
     <t>about_software</t>
   </si>
   <si>
-    <t>About the software</t>
-  </si>
-  <si>
-    <t>关于软件</t>
-  </si>
-  <si>
-    <t>關於軟體</t>
-  </si>
-  <si>
-    <t>ソフトウェアについて</t>
-  </si>
-  <si>
-    <t>소프트웨어에 대하여</t>
-  </si>
-  <si>
-    <t>Über die Software</t>
-  </si>
-  <si>
-    <t>À propos du logiciel</t>
-  </si>
-  <si>
-    <t>Acerca del software</t>
-  </si>
-  <si>
-    <t>Informazioni sul software</t>
+    <t>about</t>
+  </si>
+  <si>
+    <t>关于</t>
+  </si>
+  <si>
+    <t>關於</t>
+  </si>
+  <si>
+    <t>について</t>
+  </si>
+  <si>
+    <t>~에 대한</t>
+  </si>
+  <si>
+    <t>um</t>
+  </si>
+  <si>
+    <t>à propos</t>
+  </si>
+  <si>
+    <t>acerca de</t>
+  </si>
+  <si>
+    <t>Di</t>
   </si>
   <si>
     <t>exit_software</t>
   </si>
   <si>
-    <t>Exit the software</t>
-  </si>
-  <si>
-    <t>退出软件</t>
-  </si>
-  <si>
-    <t>退出軟體</t>
-  </si>
-  <si>
-    <t>ソフトウェアを終了してください。</t>
-  </si>
-  <si>
-    <t>소프트웨어를 종료하세요</t>
-  </si>
-  <si>
-    <t>Beenden Sie die Software</t>
-  </si>
-  <si>
-    <t>Quitter le logiciel</t>
-  </si>
-  <si>
-    <t>Salir del software</t>
-  </si>
-  <si>
-    <t>Esci dal software</t>
+    <t>quit</t>
+  </si>
+  <si>
+    <t>退出</t>
+  </si>
+  <si>
+    <t>やめる</t>
+  </si>
+  <si>
+    <t>그만두다</t>
+  </si>
+  <si>
+    <t>aufhören</t>
+  </si>
+  <si>
+    <t>quitter</t>
+  </si>
+  <si>
+    <t>abandonar</t>
+  </si>
+  <si>
+    <t>esentato</t>
   </si>
   <si>
     <t>diy_template_tool</t>
@@ -242,61 +236,58 @@
     <t>rust_installation_path</t>
   </si>
   <si>
-    <t>Rust installation path</t>
-  </si>
-  <si>
-    <t>rust安装路径</t>
-  </si>
-  <si>
-    <t>rust安裝路徑</t>
-  </si>
-  <si>
-    <t>Rustのインストールパス</t>
-  </si>
-  <si>
-    <t>Rust 설치 경로</t>
-  </si>
-  <si>
-    <t>Rust-Installationspfad</t>
-  </si>
-  <si>
-    <t>Chemin d'installation de Rust</t>
-  </si>
-  <si>
-    <t>Ruta de instalación de Rust</t>
-  </si>
-  <si>
-    <t>percorso di installazione di Rust</t>
+    <t>Rust path</t>
+  </si>
+  <si>
+    <t>rust路径</t>
+  </si>
+  <si>
+    <t>rust路徑</t>
+  </si>
+  <si>
+    <t>Rustのパス</t>
+  </si>
+  <si>
+    <t>러스트 경로</t>
+  </si>
+  <si>
+    <t>Rust-Pfad</t>
+  </si>
+  <si>
+    <t>Chemin Rust</t>
+  </si>
+  <si>
+    <t>Ruta oxidada</t>
+  </si>
+  <si>
+    <t>Percorso della ruggine</t>
   </si>
   <si>
     <t>godot_startup_file</t>
   </si>
   <si>
-    <t>Godot startup file</t>
-  </si>
-  <si>
-    <t>Godot启动文件</t>
-  </si>
-  <si>
-    <t>Godot啟動文件</t>
-  </si>
-  <si>
-    <t>Godotの起動ファイル</t>
-  </si>
-  <si>
-    <t>Godot 시작 파일</t>
-  </si>
-  <si>
-    <t>Godot-Startdatei</t>
-  </si>
-  <si>
-    <t>fichier de démarrage Godot</t>
-  </si>
-  <si>
-    <t>archivo de inicio de Godot</t>
-  </si>
-  <si>
-    <t>Risoluzione di avvio di Godot</t>
+    <t>Godot file</t>
+  </si>
+  <si>
+    <t>Godot文件</t>
+  </si>
+  <si>
+    <t>Godotファイル</t>
+  </si>
+  <si>
+    <t>고도 파일</t>
+  </si>
+  <si>
+    <t>Godot-Datei</t>
+  </si>
+  <si>
+    <t>Fichier Godot</t>
+  </si>
+  <si>
+    <t>Archivo Godot</t>
+  </si>
+  <si>
+    <t>Risoluzione Godot</t>
   </si>
   <si>
     <t>select_cargo_path</t>
@@ -479,31 +470,31 @@
     <t>start_creating_project</t>
   </si>
   <si>
-    <t>Start creating a project</t>
-  </si>
-  <si>
-    <t>开始创建项目</t>
-  </si>
-  <si>
-    <t>開始創建專案</t>
-  </si>
-  <si>
-    <t>プロジェクトの作成を開始する</t>
-  </si>
-  <si>
-    <t>프로젝트 생성을 시작하세요</t>
-  </si>
-  <si>
-    <t>Beginnen Sie mit der Erstellung eines Projekts</t>
-  </si>
-  <si>
-    <t>Commencez à créer un projet</t>
-  </si>
-  <si>
-    <t>Comienza a crear un proyecto</t>
-  </si>
-  <si>
-    <t>Inizia a creare un progetto</t>
+    <t>Create a project</t>
+  </si>
+  <si>
+    <t>创建项目</t>
+  </si>
+  <si>
+    <t>創建專案</t>
+  </si>
+  <si>
+    <t>プロジェクトを作成する</t>
+  </si>
+  <si>
+    <t>프로젝트를 생성하세요</t>
+  </si>
+  <si>
+    <t>Ein Projekt erstellen</t>
+  </si>
+  <si>
+    <t>Créer un projet</t>
+  </si>
+  <si>
+    <t>Crear un proyecto</t>
+  </si>
+  <si>
+    <t>Crea un progetto</t>
   </si>
   <si>
     <t>we_need_to_create_study_project</t>
@@ -2033,985 +2024,985 @@
         <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:10">
       <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:10">
       <c r="A6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:10">
       <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:10">
       <c r="A8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:10">
       <c r="A9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:10">
       <c r="A10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:10">
       <c r="A11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:10">
       <c r="A14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="G14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:10">
       <c r="A16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:10">
       <c r="A17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:10">
       <c r="A18" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:10">
       <c r="A19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:10">
       <c r="A20" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="I20" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="J20" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:10">
       <c r="A21" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:10">
       <c r="A22" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:10">
       <c r="A23" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="I23" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="J23" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:10">
       <c r="A24" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:10">
       <c r="A25" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="E25" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:10">
       <c r="A26" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:10">
       <c r="A27" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="J27" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:10">
       <c r="A28" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:10">
       <c r="A29" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:10">
       <c r="A30" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:10">
       <c r="A31" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="J31" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:10">
       <c r="A32" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:10">
       <c r="A33" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="G33" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="H33" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="I33" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="J33" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/godot/application/internationality/internationality.xlsx
+++ b/godot/application/internationality/internationality.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="331">
   <si>
     <t>KEYS</t>
   </si>
@@ -990,6 +990,36 @@
   </si>
   <si>
     <t>Programma di uscita</t>
+  </si>
+  <si>
+    <t>set_language</t>
+  </si>
+  <si>
+    <t>Set language</t>
+  </si>
+  <si>
+    <t>设置语言</t>
+  </si>
+  <si>
+    <t>設定語言</t>
+  </si>
+  <si>
+    <t>言語を設定</t>
+  </si>
+  <si>
+    <t>언어 설정</t>
+  </si>
+  <si>
+    <t>Sprache festlegen</t>
+  </si>
+  <si>
+    <t>Définir la langue</t>
+  </si>
+  <si>
+    <t>Establecer idioma</t>
+  </si>
+  <si>
+    <t>Imposta la lingua</t>
   </si>
 </sst>
 </file>
@@ -1933,7 +1963,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5454545454545" style="2" customWidth="1"/>
@@ -3005,6 +3035,38 @@
         <v>320</v>
       </c>
     </row>
+    <row r="34" customHeight="1" spans="1:10">
+      <c r="A34" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/godot/application/internationality/internationality.xlsx
+++ b/godot/application/internationality/internationality.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="590">
   <si>
     <t>KEYS</t>
   </si>
@@ -1020,6 +1020,783 @@
   </si>
   <si>
     <t>Imposta la lingua</t>
+  </si>
+  <si>
+    <t>godot_project_start_up_done</t>
+  </si>
+  <si>
+    <t>godot project start up done</t>
+  </si>
+  <si>
+    <t>Godot项目启动完成</t>
+  </si>
+  <si>
+    <t>Godot專案啟動完成</t>
+  </si>
+  <si>
+    <t>プロジェクト・ゴドーは無事開始されました。</t>
+  </si>
+  <si>
+    <t>프로젝트 고도가 성공적으로 실행되었습니다.</t>
+  </si>
+  <si>
+    <t>Das Projekt Godot wurde erfolgreich gestartet.</t>
+  </si>
+  <si>
+    <t>Le projet Godot a été lancé avec succès.</t>
+  </si>
+  <si>
+    <t>El proyecto Godot se lanzó con éxito.</t>
+  </si>
+  <si>
+    <t>Il progetto Godot è stato lanciato con successo.</t>
+  </si>
+  <si>
+    <t>all_operations_have_been_completed</t>
+  </si>
+  <si>
+    <t>all operations have been completed.</t>
+  </si>
+  <si>
+    <t>所有操作均已完成。</t>
+  </si>
+  <si>
+    <t>すべての作業が完了しました。</t>
+  </si>
+  <si>
+    <t>모든 작업이 완료되었습니다.</t>
+  </si>
+  <si>
+    <t>Alle Operationen sind abgeschlossen.</t>
+  </si>
+  <si>
+    <t>Toutes les opérations ont été terminées.</t>
+  </si>
+  <si>
+    <t>Todas las operaciones han finalizado.</t>
+  </si>
+  <si>
+    <t>Tutte le operazioni sono state completate.</t>
+  </si>
+  <si>
+    <t>godot_cannot_be_empty</t>
+  </si>
+  <si>
+    <t>The path to Godot cannot be empty.</t>
+  </si>
+  <si>
+    <t>Godot 的路径不能为空</t>
+  </si>
+  <si>
+    <t>Godot 的路徑不能為空</t>
+  </si>
+  <si>
+    <t>ゴドーの道は空っぽであってはならない。</t>
+  </si>
+  <si>
+    <t>고도의 경로는 비어있을 수 없습니다.</t>
+  </si>
+  <si>
+    <t>Godots Weg kann nicht leer sein.</t>
+  </si>
+  <si>
+    <t>Le chemin de Godot ne peut être vide.</t>
+  </si>
+  <si>
+    <t>El camino de Godot no puede estar vacío.</t>
+  </si>
+  <si>
+    <t>Il cammino di Godot non può essere vuoto.</t>
+  </si>
+  <si>
+    <t>rust_paths_cannot_be_empty</t>
+  </si>
+  <si>
+    <t>Rust paths cannot be empty.</t>
+  </si>
+  <si>
+    <t>Rust 的路径不能为空</t>
+  </si>
+  <si>
+    <t>Rust 的路徑不能為空</t>
+  </si>
+  <si>
+    <t>Rustのパスは空にすることはできません。</t>
+  </si>
+  <si>
+    <t>Rust 경로는 비어있을 수 없습니다.</t>
+  </si>
+  <si>
+    <t>Rust-Pfade dürfen nicht leer sein.</t>
+  </si>
+  <si>
+    <t>Les chemins Rust ne peuvent pas être vides.</t>
+  </si>
+  <si>
+    <t>Las rutas de Rust no pueden estar vacías.</t>
+  </si>
+  <si>
+    <t>I percorsi Rust non possono essere vuoti.</t>
+  </si>
+  <si>
+    <t>workspace_cannot_be_empty</t>
+  </si>
+  <si>
+    <t>The path in the workspace cannot be empty.</t>
+  </si>
+  <si>
+    <t>工作空间 的路径不能为空</t>
+  </si>
+  <si>
+    <t>工作空間 的路徑不能為空</t>
+  </si>
+  <si>
+    <t>ワークスペース内のパスは空にすることはできません。</t>
+  </si>
+  <si>
+    <t>워크스페이스의 경로는 비어있을 수 없습니다.</t>
+  </si>
+  <si>
+    <t>Der Pfad im Arbeitsbereich darf nicht leer sein.</t>
+  </si>
+  <si>
+    <t>Le chemin d'accès dans l'espace de travail ne peut pas être vide.</t>
+  </si>
+  <si>
+    <t>La ruta en el espacio de trabajo no puede estar vacía.</t>
+  </si>
+  <si>
+    <t>Il percorso nell'area di lavoro non può essere vuoto.</t>
+  </si>
+  <si>
+    <t>gdext_cannot_be_empty</t>
+  </si>
+  <si>
+    <t>The name gdext cannot be empty.</t>
+  </si>
+  <si>
+    <t>gdext的名称不能为空</t>
+  </si>
+  <si>
+    <t>gdext的名稱不能為空</t>
+  </si>
+  <si>
+    <t>gdextという名前は空にすることはできません。</t>
+  </si>
+  <si>
+    <t>gdext라는 이름은 비워둘 수 없습니다.</t>
+  </si>
+  <si>
+    <t>Der Name gdext darf nicht leer sein.</t>
+  </si>
+  <si>
+    <t>Le nom gdext ne peut pas être vide.</t>
+  </si>
+  <si>
+    <t>El nombre gdext no puede estar vacío.</t>
+  </si>
+  <si>
+    <t>Il nome gdext non può essere vuoto.</t>
+  </si>
+  <si>
+    <t>modify_cargo_toml_create_done</t>
+  </si>
+  <si>
+    <t>modify cargo toml create done</t>
+  </si>
+  <si>
+    <t>修改 cargo toml 创建完成</t>
+  </si>
+  <si>
+    <t>修改 cargo toml 創建完成</t>
+  </si>
+  <si>
+    <t>Cargo.tmlが修正され、作成されました。</t>
+  </si>
+  <si>
+    <t>Cargo.tml 파일이 수정되어 생성되었습니다.</t>
+  </si>
+  <si>
+    <t>Cargo.tml wurde geändert und erstellt.</t>
+  </si>
+  <si>
+    <t>Fichier Cargo.tml modifié et créé.</t>
+  </si>
+  <si>
+    <t>Cargo.tml modificado y creado.</t>
+  </si>
+  <si>
+    <t>File Cargo.tml modificato e creato.</t>
+  </si>
+  <si>
+    <t>modify_cargo_toml_create_fail</t>
+  </si>
+  <si>
+    <t>modify cargo toml create fail</t>
+  </si>
+  <si>
+    <t>修改 cargo toml 创建失败</t>
+  </si>
+  <si>
+    <t>修改 cargo toml 創建失敗</t>
+  </si>
+  <si>
+    <t>Cargo.tmlの作成に失敗しました。</t>
+  </si>
+  <si>
+    <t>Cargo.tml 파일 생성에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Die Erstellung der Datei Cargo.tml ist fehlgeschlagen.</t>
+  </si>
+  <si>
+    <t>La création du fichier Cargo.tml a échoué.</t>
+  </si>
+  <si>
+    <t>Error al crear Cargo.tml.</t>
+  </si>
+  <si>
+    <t>Creazione del file Cargo.tml non riuscita.</t>
+  </si>
+  <si>
+    <t>modify_lib_rs_done</t>
+  </si>
+  <si>
+    <t>modify lib rs done</t>
+  </si>
+  <si>
+    <t>修改库 rs 完成</t>
+  </si>
+  <si>
+    <t>修改庫 rs 完成</t>
+  </si>
+  <si>
+    <t>rsライブラリの修正が完了しました。</t>
+  </si>
+  <si>
+    <t>rs 라이브러리 수정이 완료되었습니다.</t>
+  </si>
+  <si>
+    <t>Die Modifizierung der rs-Bibliothek ist abgeschlossen.</t>
+  </si>
+  <si>
+    <t>La modification de la bibliothèque rs est terminée.</t>
+  </si>
+  <si>
+    <t>La modificación de la biblioteca rs ha finalizado.</t>
+  </si>
+  <si>
+    <t>La modifica della libreria rs è completa.</t>
+  </si>
+  <si>
+    <t>modify_lib_rs_fail</t>
+  </si>
+  <si>
+    <t>modify lib rs fail</t>
+  </si>
+  <si>
+    <t>修改库 rs 失败</t>
+  </si>
+  <si>
+    <t>修改庫 rs 失敗</t>
+  </si>
+  <si>
+    <t>rsライブラリの変更に失敗しました。</t>
+  </si>
+  <si>
+    <t>rs 라이브러리 수정에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Die Modifizierung der rs-Bibliothek ist fehlgeschlagen.</t>
+  </si>
+  <si>
+    <t>La modification de la bibliothèque rs a échoué.</t>
+  </si>
+  <si>
+    <t>La modificación de la biblioteca rs falló.</t>
+  </si>
+  <si>
+    <t>La modifica della libreria rs non è riuscita.</t>
+  </si>
+  <si>
+    <t>dir_godot_create_success</t>
+  </si>
+  <si>
+    <t>dir godot create success</t>
+  </si>
+  <si>
+    <t>dir godot 创建成功</t>
+  </si>
+  <si>
+    <t>dir godot 創建成功</t>
+  </si>
+  <si>
+    <t>ディレクトリ godot が正常に作成されました</t>
+  </si>
+  <si>
+    <t>dir godot이 성공적으로 생성되었습니다.</t>
+  </si>
+  <si>
+    <t>dir godot erfolgreich erstellt</t>
+  </si>
+  <si>
+    <t>répertoire godot créé avec succès</t>
+  </si>
+  <si>
+    <t>El directorio godot se creó correctamente.</t>
+  </si>
+  <si>
+    <t>dir godot creato con successo</t>
+  </si>
+  <si>
+    <t>project_godot_create_success</t>
+  </si>
+  <si>
+    <t>project.godot create success</t>
+  </si>
+  <si>
+    <t>project.godot 创建成功</t>
+  </si>
+  <si>
+    <t>project.godot 創建成功</t>
+  </si>
+  <si>
+    <t>project.godot が正常に作成されました</t>
+  </si>
+  <si>
+    <t>project.godot이 성공적으로 생성되었습니다.</t>
+  </si>
+  <si>
+    <t>project.godot wurde erfolgreich erstellt</t>
+  </si>
+  <si>
+    <t>projet.godot créé avec succès</t>
+  </si>
+  <si>
+    <t>El proyecto godot se creó correctamente.</t>
+  </si>
+  <si>
+    <t>Progetto Godot creato con successo</t>
+  </si>
+  <si>
+    <t>project_godot_create_fail</t>
+  </si>
+  <si>
+    <t>project.godot create fail</t>
+  </si>
+  <si>
+    <t>project.godot 创建失败</t>
+  </si>
+  <si>
+    <t>project.godot 建立失敗</t>
+  </si>
+  <si>
+    <t>プロジェクト.godotの作成に失敗しました。</t>
+  </si>
+  <si>
+    <t>Project.godot 생성에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Die Erstellung des Projekts „godot“ ist fehlgeschlagen.</t>
+  </si>
+  <si>
+    <t>La création du projet godot a échoué.</t>
+  </si>
+  <si>
+    <t>La creación del proyecto godot falló.</t>
+  </si>
+  <si>
+    <t>Creazione del progetto godot non riuscita.</t>
+  </si>
+  <si>
+    <t>create_file_gdextension_create_success</t>
+  </si>
+  <si>
+    <t>create file gdextension create success</t>
+  </si>
+  <si>
+    <t>创建文件 gdextension 创建成功</t>
+  </si>
+  <si>
+    <t>建立檔案 gdextension 建立成功</t>
+  </si>
+  <si>
+    <t>ファイルgdextensionが正常に作成されました。</t>
+  </si>
+  <si>
+    <t>gdextension 파일이 성공적으로 생성되었습니다.</t>
+  </si>
+  <si>
+    <t>Die Datei mit der Dateiendung gdexend wurde erfolgreich erstellt.</t>
+  </si>
+  <si>
+    <t>Le fichier gdextension a été créé avec succès.</t>
+  </si>
+  <si>
+    <t>El archivo gdextension se creó correctamente.</t>
+  </si>
+  <si>
+    <t>Il file gdextension è stato creato correttamente.</t>
+  </si>
+  <si>
+    <t>create_file_gdextension_create_fail</t>
+  </si>
+  <si>
+    <t>create file gdextension create fail</t>
+  </si>
+  <si>
+    <t>创建文件 gdextension 创建失败</t>
+  </si>
+  <si>
+    <t>建立檔案 gdextension 建立失敗</t>
+  </si>
+  <si>
+    <t>ファイルgdextensionの作成に失敗しました。</t>
+  </si>
+  <si>
+    <t>gdextension 파일 생성에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Das Erstellen der Dateierweiterung gdex ist fehlgeschlagen.</t>
+  </si>
+  <si>
+    <t>La création du fichier gdextension a échoué.</t>
+  </si>
+  <si>
+    <t>Error al crear el archivo gdextension.</t>
+  </si>
+  <si>
+    <t>La creazione del file gdextension non è riuscita.</t>
+  </si>
+  <si>
+    <t>modify_godot_projects_done</t>
+  </si>
+  <si>
+    <t>modify godot projects done</t>
+  </si>
+  <si>
+    <t>修改已完成的 Godot 项目</t>
+  </si>
+  <si>
+    <t>修改已完成的 Godot 項目</t>
+  </si>
+  <si>
+    <t>完成した Godot プロジェクトを修正する</t>
+  </si>
+  <si>
+    <t>완성된 Godot 프로젝트를 수정합니다.</t>
+  </si>
+  <si>
+    <t>Ein abgeschlossenes Godot-Projekt modifizieren</t>
+  </si>
+  <si>
+    <t>Modifier un projet Godot terminé</t>
+  </si>
+  <si>
+    <t>Modificar un proyecto Godot completado</t>
+  </si>
+  <si>
+    <t>Modificare un progetto Godot completato</t>
+  </si>
+  <si>
+    <t>is_need_create_demo</t>
+  </si>
+  <si>
+    <t>is need create demo</t>
+  </si>
+  <si>
+    <t>需要创建演示</t>
+  </si>
+  <si>
+    <t>需要建立演示</t>
+  </si>
+  <si>
+    <t>デモを作成する必要があります</t>
+  </si>
+  <si>
+    <t>데모를 제작해야 합니다.</t>
+  </si>
+  <si>
+    <t>Es muss eine Demo erstellt werden.</t>
+  </si>
+  <si>
+    <t>Une démo doit être créée.</t>
+  </si>
+  <si>
+    <t>Es necesario crear una demostración.</t>
+  </si>
+  <si>
+    <t>È necessario creare una demo</t>
+  </si>
+  <si>
+    <t>modify_godot_projects_fail</t>
+  </si>
+  <si>
+    <t>modify godot projects fail</t>
+  </si>
+  <si>
+    <t>修改 Godot 项目失败</t>
+  </si>
+  <si>
+    <t>修改 Godot 專案失敗</t>
+  </si>
+  <si>
+    <t>Godotプロジェクトの変更に失敗しました。</t>
+  </si>
+  <si>
+    <t>Godot 프로젝트 수정에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Die Änderung des Godot-Projekts ist fehlgeschlagen.</t>
+  </si>
+  <si>
+    <t>La modification du projet Godot a échoué.</t>
+  </si>
+  <si>
+    <t>La modificación del proyecto Godot falló.</t>
+  </si>
+  <si>
+    <t>La modifica del progetto Godot non è andata a buon fine.</t>
+  </si>
+  <si>
+    <t>lib_rs_append_module_success</t>
+  </si>
+  <si>
+    <t>lib.rs append module success</t>
+  </si>
+  <si>
+    <t>lib.rs 追加模块成功</t>
+  </si>
+  <si>
+    <t>lib.rs 追加模組成功</t>
+  </si>
+  <si>
+    <t>モジュールはlib.rsに正常に追加されました。</t>
+  </si>
+  <si>
+    <t>해당 모듈이 lib.rs에 성공적으로 추가되었습니다.</t>
+  </si>
+  <si>
+    <t>Das Modul wurde erfolgreich zu lib.rs hinzugefügt.</t>
+  </si>
+  <si>
+    <t>Le module a été ajouté avec succès à lib.rs.</t>
+  </si>
+  <si>
+    <t>El módulo se agregó correctamente a lib.rs.</t>
+  </si>
+  <si>
+    <t>Il modulo è stato aggiunto correttamente a lib.rs.</t>
+  </si>
+  <si>
+    <t>lib_rs_append_module_fail</t>
+  </si>
+  <si>
+    <t>lib.rs append module fail</t>
+  </si>
+  <si>
+    <t>lib.rs 追加模块失败</t>
+  </si>
+  <si>
+    <t>lib.rs 追加模組失敗</t>
+  </si>
+  <si>
+    <t>lib.rsへのモジュールの追加に失敗しました。</t>
+  </si>
+  <si>
+    <t>lib.rs에 모듈을 추가하는 데 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Das Hinzufügen von Modulen zu lib.rs ist fehlgeschlagen.</t>
+  </si>
+  <si>
+    <t>L'ajout de modules à lib.rs a échoué.</t>
+  </si>
+  <si>
+    <t>No se pudo agregar los módulos a lib.rs.</t>
+  </si>
+  <si>
+    <t>L'aggiunta dei moduli a lib.rs non è riuscita.</t>
+  </si>
+  <si>
+    <t>create_file_node_hello_done</t>
+  </si>
+  <si>
+    <t>create file node hello done</t>
+  </si>
+  <si>
+    <t>创建文件node hello 完成</t>
+  </si>
+  <si>
+    <t>建立檔案node hello 完成</t>
+  </si>
+  <si>
+    <t>ファイル「node hello」が作成されました。</t>
+  </si>
+  <si>
+    <t>"node hello" 파일이 생성되었습니다.</t>
+  </si>
+  <si>
+    <t>Die Datei "node hello" wurde erstellt.</t>
+  </si>
+  <si>
+    <t>Le fichier « node hello » a été créé.</t>
+  </si>
+  <si>
+    <t>Se ha creado el archivo "node hello".</t>
+  </si>
+  <si>
+    <t>Il file "node hello" è stato creato.</t>
+  </si>
+  <si>
+    <t>create_file_node_hello_fail</t>
+  </si>
+  <si>
+    <t>create file node hello fail</t>
+  </si>
+  <si>
+    <t>创建文件node hello 失败</t>
+  </si>
+  <si>
+    <t>建立檔案node hello 失敗</t>
+  </si>
+  <si>
+    <t>ファイルノードhelloの作成に失敗しました。</t>
+  </si>
+  <si>
+    <t>파일 노드 hello 생성에 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Das Erstellen des Dateiknotens „hello“ ist fehlgeschlagen.</t>
+  </si>
+  <si>
+    <t>La création du fichier node hello a échoué.</t>
+  </si>
+  <si>
+    <t>Error al crear el archivo node hello.</t>
+  </si>
+  <si>
+    <t>La creazione del file node hello non è riuscita.</t>
+  </si>
+  <si>
+    <t>create_main_scene_done</t>
+  </si>
+  <si>
+    <t>create main scene done</t>
+  </si>
+  <si>
+    <t>创建主场景完成</t>
+  </si>
+  <si>
+    <t>建立主場景完成</t>
+  </si>
+  <si>
+    <t>メインシーンの作成が完了しました</t>
+  </si>
+  <si>
+    <t>메인 장면 생성 완료</t>
+  </si>
+  <si>
+    <t>Hauptszene erstellt</t>
+  </si>
+  <si>
+    <t>Création de la scène principale terminée</t>
+  </si>
+  <si>
+    <t>Creación de la escena principal completada</t>
+  </si>
+  <si>
+    <t>Creazione della scena principale completata.</t>
+  </si>
+  <si>
+    <t>create_main_scene_fail</t>
+  </si>
+  <si>
+    <t>create main scene fail</t>
+  </si>
+  <si>
+    <t>创建主场景失败</t>
+  </si>
+  <si>
+    <t>建立主場景失敗</t>
+  </si>
+  <si>
+    <t>メインシーンの作成に失敗しました</t>
+  </si>
+  <si>
+    <t>메인 장면을 생성하는 데 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Hauptszene konnte nicht erstellt werden</t>
+  </si>
+  <si>
+    <t>Échec de la création de la scène principale</t>
+  </si>
+  <si>
+    <t>No se pudo crear la escena principal.</t>
+  </si>
+  <si>
+    <t>Impossibile creare la scena principale</t>
+  </si>
+  <si>
+    <t>set_as_main_scene_success</t>
+  </si>
+  <si>
+    <t>set as main scene success</t>
+  </si>
+  <si>
+    <t>设定为主要场景成功</t>
+  </si>
+  <si>
+    <t>設定為主要場景成功</t>
+  </si>
+  <si>
+    <t>メインシーンとして設定に成功しました</t>
+  </si>
+  <si>
+    <t>성공적으로 메인 장면으로 설정되었습니다.</t>
+  </si>
+  <si>
+    <t>Erfolgreich als Hauptszene etabliert</t>
+  </si>
+  <si>
+    <t>Un décor principal parfaitement établi</t>
+  </si>
+  <si>
+    <t>Se estableció con éxito como la escena principal.</t>
+  </si>
+  <si>
+    <t>Ambientato con successo come scena principale</t>
+  </si>
+  <si>
+    <t>set_as_main_scene_fail</t>
+  </si>
+  <si>
+    <t>set as main scene fail</t>
+  </si>
+  <si>
+    <t>设置为主要场景失败</t>
+  </si>
+  <si>
+    <t>設定為主要場景失敗</t>
+  </si>
+  <si>
+    <t>メインシーンとして設定する試みは失敗しました。</t>
+  </si>
+  <si>
+    <t>메인 장면으로 설정하는 데 실패했습니다.</t>
+  </si>
+  <si>
+    <t>Das Festlegen als Hauptszene schlug fehl.</t>
+  </si>
+  <si>
+    <t>Le choix de la scène principale a échoué.</t>
+  </si>
+  <si>
+    <t>La configuración como escena principal falló.</t>
+  </si>
+  <si>
+    <t>L'impostazione come scena principale non è riuscita.</t>
   </si>
 </sst>
 </file>
@@ -1963,18 +2740,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5454545454545" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.9090909090909" style="2" customWidth="1"/>
     <col min="3" max="4" width="27.5454545454545" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.8181818181818" style="2" customWidth="1"/>
-    <col min="6" max="6" width="35.7272727272727" style="2" customWidth="1"/>
-    <col min="7" max="7" width="41" style="2" customWidth="1"/>
-    <col min="8" max="8" width="50.2545454545455" style="2" customWidth="1"/>
-    <col min="9" max="9" width="48.3636363636364" style="2" customWidth="1"/>
-    <col min="10" max="10" width="71.7272727272727" style="2" customWidth="1"/>
+    <col min="5" max="5" width="71.7272727272727" style="2" customWidth="1"/>
+    <col min="6" max="6" width="58.8181818181818" style="2" customWidth="1"/>
+    <col min="7" max="7" width="80.2727272727273" style="2" customWidth="1"/>
+    <col min="8" max="8" width="78.4818181818182" style="2" customWidth="1"/>
+    <col min="9" max="9" width="80.7545454545455" style="2" customWidth="1"/>
+    <col min="10" max="10" width="101.354545454545" style="2" customWidth="1"/>
     <col min="11" max="16" width="20.6363636363636" style="2" customWidth="1"/>
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
@@ -3067,6 +3844,838 @@
         <v>330</v>
       </c>
     </row>
+    <row r="35" customHeight="1" spans="1:10">
+      <c r="A35" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:10">
+      <c r="A36" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:10">
+      <c r="A37" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:10">
+      <c r="A38" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:10">
+      <c r="A39" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:10">
+      <c r="A40" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:10">
+      <c r="A41" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:10">
+      <c r="A42" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:10">
+      <c r="A43" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:10">
+      <c r="A44" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:10">
+      <c r="A45" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:10">
+      <c r="A46" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:10">
+      <c r="A47" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:10">
+      <c r="A48" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:10">
+      <c r="A49" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:10">
+      <c r="A50" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:10">
+      <c r="A51" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:10">
+      <c r="A52" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:10">
+      <c r="A53" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:10">
+      <c r="A54" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:10">
+      <c r="A55" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:10">
+      <c r="A56" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:10">
+      <c r="A57" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:10">
+      <c r="A58" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:10">
+      <c r="A59" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:10">
+      <c r="A60" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
